--- a/1.0excel/class/304_3_5_VH_LOOKUP_index_match.xlsx
+++ b/1.0excel/class/304_3_5_VH_LOOKUP_index_match.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\ds_materials\1.0excel\class\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1922621D-5C5B-471A-A8DE-C22F52DE0C77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF317EC2-4E7E-48A4-B7CF-1A1859E1B272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="vlookups" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="10" r:id="rId2"/>
-    <sheet name="302" sheetId="9" r:id="rId3"/>
-    <sheet name="hlookup" sheetId="3" r:id="rId4"/>
-    <sheet name="index" sheetId="4" r:id="rId5"/>
-    <sheet name="match" sheetId="5" r:id="rId6"/>
-    <sheet name="index-match" sheetId="6" r:id="rId7"/>
+    <sheet name="Sheet2" sheetId="11" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="10" r:id="rId3"/>
+    <sheet name="302" sheetId="9" r:id="rId4"/>
+    <sheet name="hlookup" sheetId="3" r:id="rId5"/>
+    <sheet name="index" sheetId="4" r:id="rId6"/>
+    <sheet name="match" sheetId="5" r:id="rId7"/>
+    <sheet name="index-match" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="97">
   <si>
     <t>Below is a list of the employees who work in your company:</t>
   </si>
@@ -370,17 +370,36 @@
   <si>
     <t>usa</t>
   </si>
+  <si>
+    <t xml:space="preserve">index </t>
+  </si>
+  <si>
+    <t>match</t>
+  </si>
+  <si>
+    <t>use index</t>
+  </si>
+  <si>
+    <t>bangkok</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -558,42 +577,43 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1290,6 +1310,279 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94C2D3BE-E6C9-4310-9F19-E61CABBF2040}">
+  <dimension ref="A1:P13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.7109375" customWidth="1"/>
+    <col min="15" max="15" width="19.7109375" customWidth="1"/>
+    <col min="16" max="16" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="A1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="16">
+        <v>56815</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="13">
+        <v>13836</v>
+      </c>
+      <c r="E2" s="13">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="16">
+        <v>51186</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="13">
+        <v>11771</v>
+      </c>
+      <c r="E3" s="13">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="16">
+        <v>51511</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="13">
+        <v>13046</v>
+      </c>
+      <c r="E4" s="13">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="16">
+        <v>50890</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="13">
+        <v>18276</v>
+      </c>
+      <c r="E5" s="13">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="16">
+        <v>53700</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="13">
+        <v>19327</v>
+      </c>
+      <c r="E6" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" s="16">
+        <v>55879</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="13">
+        <v>18996</v>
+      </c>
+      <c r="E7" s="13">
+        <v>35</v>
+      </c>
+      <c r="M7" s="25" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="16">
+        <v>59848</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="13">
+        <v>10387</v>
+      </c>
+      <c r="E8" s="13">
+        <v>25</v>
+      </c>
+      <c r="N8" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="O8">
+        <f>MATCH(N8,C1:C13,0)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" s="16">
+        <v>58369</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="13">
+        <v>12566</v>
+      </c>
+      <c r="E9" s="13">
+        <v>37</v>
+      </c>
+      <c r="P9" t="str" cm="1">
+        <f t="array" ref="P9">INDEX(B1:B13,O8)</f>
+        <v>Thomas Bettle</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="16">
+        <v>50217</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="13">
+        <v>16406</v>
+      </c>
+      <c r="E10" s="13">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="16">
+        <v>50695</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="13">
+        <v>15784</v>
+      </c>
+      <c r="E11" s="13">
+        <v>43</v>
+      </c>
+      <c r="P11" t="str">
+        <f>INDEX(B1:B13,MATCH(N8,C1:C13,0))</f>
+        <v>Thomas Bettle</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="16">
+        <v>59673</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="13">
+        <v>10959</v>
+      </c>
+      <c r="E12" s="13">
+        <v>30</v>
+      </c>
+      <c r="I12" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="J12" t="str">
+        <f>INDEX(B1:B13,7)</f>
+        <v>Michael Kaye</v>
+      </c>
+      <c r="K12" t="str">
+        <f>INDEX(C1:C13,7)</f>
+        <v>Capetown</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="16">
+        <v>52130</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="13">
+        <v>14562</v>
+      </c>
+      <c r="E13" s="13">
+        <v>32</v>
+      </c>
+      <c r="I13" s="25" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F03CEF6-82A2-475E-A1E1-10A351765E11}">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1530,7 +1823,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
@@ -1726,7 +2019,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
@@ -2093,7 +2386,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
@@ -2191,7 +2484,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
@@ -2292,7 +2585,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>

--- a/1.0excel/class/304_3_5_VH_LOOKUP_index_match.xlsx
+++ b/1.0excel/class/304_3_5_VH_LOOKUP_index_match.xlsx
@@ -2,25 +2,27 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\ds_materials\1.0excel\class\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF317EC2-4E7E-48A4-B7CF-1A1859E1B272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA4B1205-B04F-435C-A20C-A9413BD1E8F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="vlookups" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="11" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="10" r:id="rId3"/>
-    <sheet name="302" sheetId="9" r:id="rId4"/>
-    <sheet name="hlookup" sheetId="3" r:id="rId5"/>
-    <sheet name="index" sheetId="4" r:id="rId6"/>
-    <sheet name="match" sheetId="5" r:id="rId7"/>
-    <sheet name="index-match" sheetId="6" r:id="rId8"/>
+    <sheet name="Sheet4" sheetId="13" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="12" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="10" r:id="rId5"/>
+    <sheet name="302" sheetId="9" r:id="rId6"/>
+    <sheet name="hlookup" sheetId="3" r:id="rId7"/>
+    <sheet name="index" sheetId="4" r:id="rId8"/>
+    <sheet name="match" sheetId="5" r:id="rId9"/>
+    <sheet name="index-match" sheetId="6" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="94">
   <si>
     <t>Below is a list of the employees who work in your company:</t>
   </si>
@@ -371,28 +373,26 @@
     <t>usa</t>
   </si>
   <si>
-    <t xml:space="preserve">index </t>
-  </si>
-  <si>
-    <t>match</t>
-  </si>
-  <si>
-    <t>use index</t>
-  </si>
-  <si>
-    <t>bangkok</t>
+    <t>eric green</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -577,42 +577,43 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -918,6 +919,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:K23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -932,12 +934,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
       <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:11">
@@ -1309,22 +1311,122 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <sheetPr codeName="Sheet10"/>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="2"/>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="4">
+        <v>9584423</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="4">
+        <v>5034521</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="4">
+        <v>9543669</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="4">
+        <v>9995553</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="4">
+        <v>8595323</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="4">
+        <v>9359305</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="5"/>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94C2D3BE-E6C9-4310-9F19-E61CABBF2040}">
-  <dimension ref="A1:P13"/>
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" customWidth="1"/>
     <col min="10" max="10" width="16.7109375" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" customWidth="1"/>
     <col min="15" max="15" width="19.7109375" customWidth="1"/>
     <col min="16" max="16" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:15">
       <c r="A1" s="14" t="s">
         <v>1</v>
       </c>
@@ -1340,8 +1442,14 @@
       <c r="E1" s="11" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="G1" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="16">
         <v>56815</v>
       </c>
@@ -1357,8 +1465,15 @@
       <c r="E2" s="13">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="G2">
+        <v>51511</v>
+      </c>
+      <c r="H2">
+        <f>VLOOKUP(G2,$A$1:$E$13,4,0)</f>
+        <v>13046</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="16">
         <v>51186</v>
       </c>
@@ -1374,8 +1489,15 @@
       <c r="E3" s="13">
         <v>32</v>
       </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="G3">
+        <v>50217</v>
+      </c>
+      <c r="H3">
+        <f>VLOOKUP(G3,$A$1:$E$13,4,0)</f>
+        <v>16406</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="16">
         <v>51511</v>
       </c>
@@ -1392,7 +1514,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:15">
       <c r="A5" s="16">
         <v>50890</v>
       </c>
@@ -1408,8 +1530,11 @@
       <c r="E5" s="13">
         <v>32</v>
       </c>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="H5" s="26" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="16">
         <v>53700</v>
       </c>
@@ -1425,8 +1550,15 @@
       <c r="E6" s="13">
         <v>26</v>
       </c>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="G6">
+        <v>50217</v>
+      </c>
+      <c r="H6" t="str">
+        <f>VLOOKUP(G6,A1:E13,2,0)</f>
+        <v>Eric Green</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="16">
         <v>55879</v>
       </c>
@@ -1442,11 +1574,11 @@
       <c r="E7" s="13">
         <v>35</v>
       </c>
-      <c r="M7" s="25" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="M7" s="24"/>
+      <c r="N7" s="26"/>
+      <c r="O7" s="26"/>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="16">
         <v>59848</v>
       </c>
@@ -1462,15 +1594,18 @@
       <c r="E8" s="13">
         <v>25</v>
       </c>
-      <c r="N8" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="O8">
-        <f>MATCH(N8,C1:C13,0)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="G8" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="H8" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="J8" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="N8" s="24"/>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="16">
         <v>58369</v>
       </c>
@@ -1486,12 +1621,15 @@
       <c r="E9" s="13">
         <v>37</v>
       </c>
-      <c r="P9" t="str" cm="1">
-        <f t="array" ref="P9">INDEX(B1:B13,O8)</f>
-        <v>Thomas Bettle</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="G9" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="H9" t="str">
+        <f>VLOOKUP(G9,B1:E13,2,0)</f>
+        <v>Warsaw</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="16">
         <v>50217</v>
       </c>
@@ -1507,8 +1645,17 @@
       <c r="E10" s="13">
         <v>42</v>
       </c>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="K10" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="L10" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="M10" s="26" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="16">
         <v>50695</v>
       </c>
@@ -1524,12 +1671,19 @@
       <c r="E11" s="13">
         <v>43</v>
       </c>
-      <c r="P11" t="str">
-        <f>INDEX(B1:B13,MATCH(N8,C1:C13,0))</f>
-        <v>Thomas Bettle</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="K11">
+        <v>50217</v>
+      </c>
+      <c r="L11" t="str">
+        <f>HLOOKUP(K11,A16:M20,2,0)</f>
+        <v>Eric Green</v>
+      </c>
+      <c r="M11">
+        <f>HLOOKUP(L11,A17:M20,3,0)</f>
+        <v>16406</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="16">
         <v>59673</v>
       </c>
@@ -1545,19 +1699,9 @@
       <c r="E12" s="13">
         <v>30</v>
       </c>
-      <c r="I12" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="J12" t="str">
-        <f>INDEX(B1:B13,7)</f>
-        <v>Michael Kaye</v>
-      </c>
-      <c r="K12" t="str">
-        <f>INDEX(C1:C13,7)</f>
-        <v>Capetown</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="I12" s="24"/>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="16">
         <v>52130</v>
       </c>
@@ -1573,8 +1717,449 @@
       <c r="E13" s="13">
         <v>32</v>
       </c>
-      <c r="I13" s="25" t="s">
-        <v>94</v>
+      <c r="I13" s="24"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="16">
+        <v>56815</v>
+      </c>
+      <c r="C16" s="16">
+        <v>51186</v>
+      </c>
+      <c r="D16" s="16">
+        <v>51511</v>
+      </c>
+      <c r="E16" s="16">
+        <v>50890</v>
+      </c>
+      <c r="F16" s="16">
+        <v>53700</v>
+      </c>
+      <c r="G16" s="16">
+        <v>55879</v>
+      </c>
+      <c r="H16" s="16">
+        <v>59848</v>
+      </c>
+      <c r="I16" s="16">
+        <v>58369</v>
+      </c>
+      <c r="J16" s="16">
+        <v>50217</v>
+      </c>
+      <c r="K16" s="16">
+        <v>50695</v>
+      </c>
+      <c r="L16" s="16">
+        <v>59673</v>
+      </c>
+      <c r="M16" s="16">
+        <v>52130</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L17" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="M17" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I18" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="K18" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="L18" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="M18" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="13">
+        <v>13836</v>
+      </c>
+      <c r="C19" s="13">
+        <v>11771</v>
+      </c>
+      <c r="D19" s="13">
+        <v>13046</v>
+      </c>
+      <c r="E19" s="13">
+        <v>18276</v>
+      </c>
+      <c r="F19" s="13">
+        <v>19327</v>
+      </c>
+      <c r="G19" s="13">
+        <v>18996</v>
+      </c>
+      <c r="H19" s="13">
+        <v>10387</v>
+      </c>
+      <c r="I19" s="13">
+        <v>12566</v>
+      </c>
+      <c r="J19" s="13">
+        <v>16406</v>
+      </c>
+      <c r="K19" s="13">
+        <v>15784</v>
+      </c>
+      <c r="L19" s="13">
+        <v>10959</v>
+      </c>
+      <c r="M19" s="13">
+        <v>14562</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="13">
+        <v>25</v>
+      </c>
+      <c r="C20" s="13">
+        <v>32</v>
+      </c>
+      <c r="D20" s="13">
+        <v>35</v>
+      </c>
+      <c r="E20" s="13">
+        <v>32</v>
+      </c>
+      <c r="F20" s="13">
+        <v>26</v>
+      </c>
+      <c r="G20" s="13">
+        <v>35</v>
+      </c>
+      <c r="H20" s="13">
+        <v>25</v>
+      </c>
+      <c r="I20" s="13">
+        <v>37</v>
+      </c>
+      <c r="J20" s="13">
+        <v>42</v>
+      </c>
+      <c r="K20" s="13">
+        <v>43</v>
+      </c>
+      <c r="L20" s="13">
+        <v>30</v>
+      </c>
+      <c r="M20" s="13">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDE410C7-658B-464D-BD66-EB7C3C00A45A}">
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="16">
+        <v>56815</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="13">
+        <v>13836</v>
+      </c>
+      <c r="E2" s="13">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="16">
+        <v>51186</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="13">
+        <v>11771</v>
+      </c>
+      <c r="E3" s="13">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="16">
+        <v>51511</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="13">
+        <v>13046</v>
+      </c>
+      <c r="E4" s="13">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="16">
+        <v>50890</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="13">
+        <v>18276</v>
+      </c>
+      <c r="E5" s="13">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="16">
+        <v>53700</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="13">
+        <v>19327</v>
+      </c>
+      <c r="E6" s="13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="16">
+        <v>55879</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="13">
+        <v>18996</v>
+      </c>
+      <c r="E7" s="13">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="16">
+        <v>59848</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="13">
+        <v>10387</v>
+      </c>
+      <c r="E8" s="13">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="16">
+        <v>58369</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="13">
+        <v>12566</v>
+      </c>
+      <c r="E9" s="13">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="16">
+        <v>50217</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="13">
+        <v>16406</v>
+      </c>
+      <c r="E10" s="13">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="16">
+        <v>50695</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="13">
+        <v>15784</v>
+      </c>
+      <c r="E11" s="13">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="16">
+        <v>59673</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="13">
+        <v>10959</v>
+      </c>
+      <c r="E12" s="13">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="16">
+        <v>52130</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="13">
+        <v>14562</v>
+      </c>
+      <c r="E13" s="13">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1582,8 +2167,47 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22D721FA-360E-411E-800B-19F3660BF8FB}">
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="C4:E5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="4" max="4" width="19.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="3:5">
+      <c r="C4" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="3:5">
+      <c r="C5">
+        <v>52130</v>
+      </c>
+      <c r="D5" t="str">
+        <f>VLOOKUP(C5,Sheet2!A1:E13,2,0)</f>
+        <v>Christopher Fallon</v>
+      </c>
+      <c r="E5">
+        <f>VLOOKUP(C5,Sheet2!A1:E13,4,0)</f>
+        <v>14562</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F03CEF6-82A2-475E-A1E1-10A351765E11}">
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1823,8 +2447,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -2019,8 +2644,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:K15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -2386,8 +3012,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData>
@@ -2484,8 +3111,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:G12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData>
@@ -2583,101 +3211,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B1" s="2"/>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="4">
-        <v>9584423</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="4">
-        <v>5034521</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="4">
-        <v>9543669</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="4">
-        <v>9995553</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="4">
-        <v>8595323</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="4">
-        <v>9359305</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B11" s="5"/>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>